--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -1491,7 +1491,7 @@
     <t>bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite|5.3.0}
+    <t xml:space="preserve">Extension {bodySite|5.4.0}
 </t>
   </si>
   <si>
